--- a/Result/profitability/6187.xlsx
+++ b/Result/profitability/6187.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6525</v>
+        <v>4.05</v>
       </c>
       <c r="N2" t="n">
-        <v>51.04375</v>
+        <v>51.90750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.095</v>
+        <v>3.58</v>
       </c>
       <c r="N3" t="n">
-        <v>49.63375000000001</v>
+        <v>49.7425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>2.71375</v>
+        <v>3.33</v>
       </c>
       <c r="N4" t="n">
-        <v>48.06</v>
+        <v>47.35125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>2.30875</v>
+        <v>2.85125</v>
       </c>
       <c r="N5" t="n">
-        <v>43.47125</v>
+        <v>43.82375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8075</v>
+        <v>2.32375</v>
       </c>
       <c r="N6" t="n">
-        <v>40.3375</v>
+        <v>41.13500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.32</v>
+        <v>1.9625</v>
       </c>
       <c r="N7" t="n">
-        <v>39.7825</v>
+        <v>39</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9512500000000002</v>
+        <v>1.5925</v>
       </c>
       <c r="N8" t="n">
-        <v>36.88625</v>
+        <v>37.26000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6637500000000002</v>
+        <v>0.6637500000000003</v>
       </c>
       <c r="N12" t="n">
         <v>35.94</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F75" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>783</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>33.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>174</v>
+      </c>
+      <c r="J75" t="n">
+        <v>957</v>
+      </c>
+      <c r="K75" t="n">
+        <v>827</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.65875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53.765</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.522255192878338</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.990000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05774430281962162</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.043269230769231</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0542829643888354</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
